--- a/main/statistics/PlayerData.xlsx
+++ b/main/statistics/PlayerData.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -647,6 +647,80 @@
       <c r="G6" t="inlineStr">
         <is>
           <t>d</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>mortrpestl</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BLGbGZYCb </t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>vY</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2aYHp.sgwdPtA7fNXO</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>test67</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>bYCbe3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Fh</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>VBcHC7Fette7aBbxeD</t>
         </is>
       </c>
     </row>
